--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/机房机柜信息表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/机房机柜信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,11 +481,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -505,11 +501,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -529,11 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -553,11 +541,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -567,7 +551,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>POD01</t>
+          <t>POD05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -580,14 +564,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>V1.8_20260613173932_DRB</t>
+          <t>草稿</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>POD02</t>
+          <t>POD06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -600,14 +584,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>V1.8_20260613173932_DRB</t>
+          <t>草稿</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>POD03</t>
+          <t>POD07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -620,14 +604,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>V1.8_20260613173932_DRB</t>
+          <t>草稿</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>POD04</t>
+          <t>POD08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -640,7 +624,323 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
+          <t>草稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>POD09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>草稿</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>POD01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>V1.8_20260613173932_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>POD02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>V1.8_20260613173932_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>POD03</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>V1.8_20260613173932_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>POD04</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>V1.8_20260613173932_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>POD01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>POD02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>POD03</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>POD04</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>POD05</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>POD06</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>POD07</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>POD08</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>POD09</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
         </is>
       </c>
     </row>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/机房机柜信息表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/机房机柜信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -741,11 +741,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -765,11 +761,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -789,11 +781,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -813,11 +801,7 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -837,11 +821,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -861,11 +841,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -885,11 +861,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -909,11 +881,7 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>V2.2_20260614213043_DRB</t>
@@ -933,14 +901,226 @@
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>POD01</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
         <is>
           <t>自动解析</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>V2.2_20260614213043_DRB</t>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>POD02</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>POD03</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>POD04</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>POD05</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>POD06</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>POD07</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>POD08</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>POD09</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
         </is>
       </c>
     </row>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/机房机柜信息表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/机房机柜信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,7 +481,11 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -501,7 +505,11 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -521,7 +529,11 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -541,7 +553,11 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -561,7 +577,11 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -581,7 +601,11 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -601,7 +625,11 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -621,7 +649,11 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -641,7 +673,11 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>自动解析</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>草稿</t>
@@ -921,11 +957,7 @@
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -945,11 +977,7 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -969,11 +997,7 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -993,11 +1017,7 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -1017,11 +1037,7 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -1041,11 +1057,7 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -1065,11 +1077,7 @@
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -1089,11 +1097,7 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
@@ -1113,14 +1117,190 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>自动解析</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>POD01</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>POD02</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>POD03</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>POD04</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>POD05</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>POD06</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>POD07</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>POD08</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>POD09</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
         </is>
       </c>
     </row>
